--- a/artfynd/A 41608-2026 artfynd.xlsx
+++ b/artfynd/A 41608-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858029</v>
       </c>
       <c r="B2" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41608-2026 artfynd.xlsx
+++ b/artfynd/A 41608-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858029</v>
       </c>
       <c r="B2" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41608-2026 artfynd.xlsx
+++ b/artfynd/A 41608-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858029</v>
       </c>
       <c r="B2" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41608-2026 artfynd.xlsx
+++ b/artfynd/A 41608-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858029</v>
       </c>
       <c r="B2" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857932</v>
       </c>
       <c r="B3" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41608-2026 artfynd.xlsx
+++ b/artfynd/A 41608-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858029</v>
       </c>
       <c r="B2" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857932</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41608-2026 artfynd.xlsx
+++ b/artfynd/A 41608-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858029</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41608-2026 artfynd.xlsx
+++ b/artfynd/A 41608-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858029</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857932</v>
       </c>
       <c r="B3" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41608-2026 artfynd.xlsx
+++ b/artfynd/A 41608-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858029</v>
       </c>
       <c r="B2" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41608-2026 artfynd.xlsx
+++ b/artfynd/A 41608-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858029</v>
       </c>
       <c r="B2" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857932</v>
       </c>
       <c r="B3" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41608-2026 artfynd.xlsx
+++ b/artfynd/A 41608-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858029</v>
       </c>
       <c r="B2" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 41608-2026 artfynd.xlsx
+++ b/artfynd/A 41608-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136858029</v>
       </c>
       <c r="B2" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136857932</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
